--- a/傷病手当金算定表_修正版.xlsx
+++ b/傷病手当金算定表_修正版.xlsx
@@ -2614,15 +2614,15 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A6:B6"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="C5:D5"/>
+    <mergeCell ref="D6:F6"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D6:F6"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A6:B6"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="A13:A20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -2644,7 +2644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="39" min="1" max="1"/>
@@ -4246,11 +4246,11 @@
           <t>法定給付 計</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
+      <c r="B37" s="57" t="n"/>
+      <c r="C37" s="57" t="n"/>
+      <c r="D37" s="57" t="n"/>
+      <c r="E37" s="57" t="n"/>
+      <c r="F37" s="44" t="n"/>
       <c r="G37" s="54">
         <f>SUMIFS(G6:G35,$D$6:$D$35,"法定")</f>
         <v/>
@@ -4275,11 +4275,11 @@
           <t>附加給付 計</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-      <c r="F38" s="2" t="n"/>
+      <c r="B38" s="57" t="n"/>
+      <c r="C38" s="57" t="n"/>
+      <c r="D38" s="57" t="n"/>
+      <c r="E38" s="57" t="n"/>
+      <c r="F38" s="44" t="n"/>
       <c r="G38" s="54">
         <f>SUMIFS(G6:G35,$D$6:$D$35,"附加")</f>
         <v/>
@@ -4304,11 +4304,11 @@
           <t>合　計</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n"/>
-      <c r="C39" s="1" t="n"/>
-      <c r="D39" s="1" t="n"/>
-      <c r="E39" s="1" t="n"/>
-      <c r="F39" s="1" t="n"/>
+      <c r="B39" s="57" t="n"/>
+      <c r="C39" s="57" t="n"/>
+      <c r="D39" s="57" t="n"/>
+      <c r="E39" s="57" t="n"/>
+      <c r="F39" s="44" t="n"/>
       <c r="G39" s="55">
         <f>SUM(G37:G38)</f>
         <v/>
@@ -4327,6 +4327,7 @@
       </c>
       <c r="K39" s="55" t="n"/>
     </row>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
@@ -4356,13 +4357,18 @@
         <v/>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="40" t="inlineStr">
         <is>
-          <t>・基幹の「調整額」欄は、障害年金等との調整がある場合のみマイナスで追加入力します（本表の調整額は報酬との調整額）。</t>
-        </is>
-      </c>
-    </row>
+          <t>・基幹システムには、標準支給額（日額×日数）を入れ、報酬との調整分は「調整額」にマイナスで入力します。最終給付額が差引支給額と一致するか確認してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A38:F38"/>
